--- a/apps/docs/public/generated/examples/showcase/renewal-ops-workbook/artifact/renewal-ops-workbook.xlsx
+++ b/apps/docs/public/generated/examples/showcase/renewal-ops-workbook/artifact/renewal-ops-workbook.xlsx
@@ -212,10 +212,10 @@
     <t>amelia_wiegand25@hotmail.com</t>
   </si>
   <si>
-    <t>Portfolio total</t>
-  </si>
-  <si>
-    <t>Renewal target</t>
+    <t>Current ARR total</t>
+  </si>
+  <si>
+    <t>Target ARR total</t>
   </si>
 </sst>
 </file>
@@ -227,20 +227,36 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF1E3A8A"/>
+    </font>
+    <font>
+      <color rgb="FF64748B"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF854D0E"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF475569"/>
     </font>
     <font>
       <u/>
-      <color rgb="FF0563C1"/>
+      <color rgb="FF64748B"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF334155"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,12 +268,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE9E9E9"/>
+        <fgColor rgb="FFE0F2FE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E8F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -307,44 +338,44 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -390,7 +421,7 @@
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
@@ -456,7 +487,7 @@
         <v>913906</v>
       </c>
       <c r="G2" s="6">
-        <v>0.005160501268128392</v>
+        <f>IF((E2&gt;0),((F2/E2)-1),0)</f>
       </c>
       <c r="H2" s="7" t="s">
         <v>15</v>
@@ -494,7 +525,7 @@
         <v>253809</v>
       </c>
       <c r="G3" s="6">
-        <v>0.40957231160551144</v>
+        <f>IF((E3&gt;0),((F3/E3)-1),0)</f>
       </c>
       <c r="H3" s="7" t="s">
         <v>22</v>
@@ -532,7 +563,7 @@
         <v>554292</v>
       </c>
       <c r="G4" s="6">
-        <v>0.13779576856206233</v>
+        <f>IF((E4&gt;0),((F4/E4)-1),0)</f>
       </c>
       <c r="H4" s="7" t="s">
         <v>15</v>
@@ -570,7 +601,7 @@
         <v>1382992</v>
       </c>
       <c r="G5" s="6">
-        <v>0.07095277403927325</v>
+        <f>IF((E5&gt;0),((F5/E5)-1),0)</f>
       </c>
       <c r="H5" s="7" t="s">
         <v>32</v>
@@ -608,7 +639,7 @@
         <v>908011</v>
       </c>
       <c r="G6" s="6">
-        <v>-0.0870471864200919</v>
+        <f>IF((E6&gt;0),((F6/E6)-1),0)</f>
       </c>
       <c r="H6" s="7" t="s">
         <v>22</v>
@@ -646,7 +677,7 @@
         <v>660566</v>
       </c>
       <c r="G7" s="6">
-        <v>0.16202109899852757</v>
+        <f>IF((E7&gt;0),((F7/E7)-1),0)</f>
       </c>
       <c r="H7" s="7" t="s">
         <v>32</v>
@@ -684,7 +715,7 @@
         <v>848349</v>
       </c>
       <c r="G8" s="6">
-        <v>0.13700196212982219</v>
+        <f>IF((E8&gt;0),((F8/E8)-1),0)</f>
       </c>
       <c r="H8" s="7" t="s">
         <v>32</v>
@@ -722,7 +753,7 @@
         <v>397547</v>
       </c>
       <c r="G9" s="6">
-        <v>0.2653398348727807</v>
+        <f>IF((E9&gt;0),((F9/E9)-1),0)</f>
       </c>
       <c r="H9" s="7" t="s">
         <v>15</v>
@@ -760,7 +791,7 @@
         <v>344031</v>
       </c>
       <c r="G10" s="6">
-        <v>-0.19497042250884522</v>
+        <f>IF((E10&gt;0),((F10/E10)-1),0)</f>
       </c>
       <c r="H10" s="7" t="s">
         <v>22</v>
@@ -798,7 +829,7 @@
         <v>620563</v>
       </c>
       <c r="G11" s="6">
-        <v>-0.0688361107859996</v>
+        <f>IF((E11&gt;0),((F11/E11)-1),0)</f>
       </c>
       <c r="H11" s="7" t="s">
         <v>32</v>
@@ -836,7 +867,7 @@
         <v>482532</v>
       </c>
       <c r="G12" s="6">
-        <v>0.3890129882092852</v>
+        <f>IF((E12&gt;0),((F12/E12)-1),0)</f>
       </c>
       <c r="H12" s="7" t="s">
         <v>15</v>
@@ -874,7 +905,7 @@
         <v>979180</v>
       </c>
       <c r="G13" s="6">
-        <v>0.013146758215947907</v>
+        <f>IF((E13&gt;0),((F13/E13)-1),0)</f>
       </c>
       <c r="H13" s="7" t="s">
         <v>22</v>
@@ -912,7 +943,7 @@
         <v>1229785</v>
       </c>
       <c r="G14" s="6">
-        <v>-0.039772097301365994</v>
+        <f>IF((E14&gt;0),((F14/E14)-1),0)</f>
       </c>
       <c r="H14" s="7" t="s">
         <v>22</v>
@@ -950,7 +981,7 @@
         <v>272410</v>
       </c>
       <c r="G15" s="6">
-        <v>-0.09769928388306293</v>
+        <f>IF((E15&gt;0),((F15/E15)-1),0)</f>
       </c>
       <c r="H15" s="7" t="s">
         <v>32</v>
@@ -969,39 +1000,25 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="E16" s="11" t="s">
+      <c r="A16" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="E16" s="12">
+        <f>SUM(E2:E15)</f>
+      </c>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="11" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="E17" s="12">
-        <f>SUM(E2:E15)</f>
-      </c>
+      <c r="E17" s="11"/>
       <c r="F17" s="13">
         <f>SUM(F2:F15)</f>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" password="F9A3" selectLockedCells="1"/>
-  <hyperlinks>
-    <hyperlink ref="K2" tooltip="Email sponsor" r:id="rIdHyperlink1"/>
-    <hyperlink ref="K3" tooltip="Email sponsor" r:id="rIdHyperlink2"/>
-    <hyperlink ref="K4" tooltip="Email sponsor" r:id="rIdHyperlink3"/>
-    <hyperlink ref="K5" tooltip="Email sponsor" r:id="rIdHyperlink4"/>
-    <hyperlink ref="K6" tooltip="Email sponsor" r:id="rIdHyperlink5"/>
-    <hyperlink ref="K7" tooltip="Email sponsor" r:id="rIdHyperlink6"/>
-    <hyperlink ref="K8" tooltip="Email sponsor" r:id="rIdHyperlink7"/>
-    <hyperlink ref="K9" tooltip="Email sponsor" r:id="rIdHyperlink8"/>
-    <hyperlink ref="K10" tooltip="Email sponsor" r:id="rIdHyperlink9"/>
-    <hyperlink ref="K11" tooltip="Email sponsor" r:id="rIdHyperlink10"/>
-    <hyperlink ref="K12" tooltip="Email sponsor" r:id="rIdHyperlink11"/>
-    <hyperlink ref="K13" tooltip="Email sponsor" r:id="rIdHyperlink12"/>
-    <hyperlink ref="K14" tooltip="Email sponsor" r:id="rIdHyperlink13"/>
-    <hyperlink ref="K15" tooltip="Email sponsor" r:id="rIdHyperlink14"/>
-  </hyperlinks>
   <conditionalFormatting sqref="G2:G15">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>(F2&lt;E2)</formula>
@@ -1026,5 +1043,21 @@
       <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" tooltip="Email sponsor" r:id="rIdHyperlink1"/>
+    <hyperlink ref="K3" tooltip="Email sponsor" r:id="rIdHyperlink2"/>
+    <hyperlink ref="K4" tooltip="Email sponsor" r:id="rIdHyperlink3"/>
+    <hyperlink ref="K5" tooltip="Email sponsor" r:id="rIdHyperlink4"/>
+    <hyperlink ref="K6" tooltip="Email sponsor" r:id="rIdHyperlink5"/>
+    <hyperlink ref="K7" tooltip="Email sponsor" r:id="rIdHyperlink6"/>
+    <hyperlink ref="K8" tooltip="Email sponsor" r:id="rIdHyperlink7"/>
+    <hyperlink ref="K9" tooltip="Email sponsor" r:id="rIdHyperlink8"/>
+    <hyperlink ref="K10" tooltip="Email sponsor" r:id="rIdHyperlink9"/>
+    <hyperlink ref="K11" tooltip="Email sponsor" r:id="rIdHyperlink10"/>
+    <hyperlink ref="K12" tooltip="Email sponsor" r:id="rIdHyperlink11"/>
+    <hyperlink ref="K13" tooltip="Email sponsor" r:id="rIdHyperlink12"/>
+    <hyperlink ref="K14" tooltip="Email sponsor" r:id="rIdHyperlink13"/>
+    <hyperlink ref="K15" tooltip="Email sponsor" r:id="rIdHyperlink14"/>
+  </hyperlinks>
 </worksheet>
 </file>